--- a/per-stock/ANET/financials.xlsx
+++ b/per-stock/ANET/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>178764283904</v>
+        <v>213643264000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166415794176</v>
+        <v>201295708160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48.78694</v>
+        <v>58.106163</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.93581</v>
+        <v>38.08983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.410519</v>
+        <v>22.002623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4362237440</v>
+        <v>5278100000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141.97</v>
+        <v>169.67</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B41:E41)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D34</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C34</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B34</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B34:E34)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B4:E4)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1686,7 +2154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2711,7 +3179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4103,7 +4571,1505 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1259200000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1256500000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1259200000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1256800000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1256600000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1259200000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1256500000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1259200000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1256800000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1256600000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>12797500000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>11954400000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>11186800000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>10165300000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>9794200000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>13487100000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>12370500000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>11907100000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>10901600000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>10119100000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>11996600000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>11010500000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>10518200000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>9452100000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>9154700000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12797500000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>11954400000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>11186800000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>10165300000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>9794200000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>13487100000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>12370500000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>11907100000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>10901600000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>10119100000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>13487100000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>12370500000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>11907100000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>10901600000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>10119100000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>13487100000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>12370500000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>11907100000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10901600000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>10119100000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>13487100000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>12370500000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>11907100000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>10901600000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>10119100000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-19300000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-1900000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-19300000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-1900000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>10469900000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>9446600000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>9115100000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>8262100000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>7569200000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3036400000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2911800000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2784100000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2635600000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2551700000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8169400000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>7078100000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>6141700000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5632600000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4395500000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1609300000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1701600000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1475100000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1581200000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1273900000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>320100000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>331800000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>309600000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>307100000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>257800000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n">
+        <v>116604000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1289200000</v>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>1165500000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1274100000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1016100000</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1064100000</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1289200000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1369800000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1165500000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1274100000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1016100000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6560100000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>5376500000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>4666600000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>4051400000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>3121600000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>600700000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>246800000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>193900000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>339200000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>147600000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4909500000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>4002600000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3520700000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2787600000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2072700000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>4909500000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>4002600000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>3520700000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2787600000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2072700000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>147847000</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>107545000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1049900000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1127100000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>952000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>924600000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>901300000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>441500000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>475400000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>471000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>380700000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>263100000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>608400000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>651700000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>481000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>543900000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>638200000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>249100000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>249100000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>608400000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>651700000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>481000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>543900000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>389100000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>21656500000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>19448600000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>18048800000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>16534200000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>14514600000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>3099800000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>3061600000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>2864000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3030700000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2238300000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>272700000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>668800000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>305700000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>339600000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>245200000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1887200000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1773600000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1665400000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1802500000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1544300000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1887200000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1773600000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1665400000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1802500000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1544300000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>689600000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>416100000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>720300000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>736300000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>324900000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>273500000</v>
+      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>304100000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>319800000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>56400000</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>62008000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>416100000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>416100000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>416200000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>416500000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>268500000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>250300000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>203100000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>172600000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>152300000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>123900000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>-256400000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>-248700000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>-240800000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-233400000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>-227400000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>506700000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>451800000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>413400000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>385700000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>351300000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>38200000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>38400000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>34800000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>151800000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>107900000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>81100000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>58100000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>32900000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>269400000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>258200000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>248000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>243200000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>236300000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>18556700000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>16387000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>15184800000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>13503500000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>12276300000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>1433500000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>976400000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>733500000</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>632292000</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>434988000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1899700000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1510000000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>632300000</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>113705000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>2380000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>2247100000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>2155700000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2059100000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1957300000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1568900000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1635900000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1505100000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1457900000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1381100000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>811100000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>611200000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>650600000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>601200000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>576200000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1923800000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1886900000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1489400000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1623600000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1435900000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1923800000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1886900000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1489400000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1623600000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1435900000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>12353200000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>10743000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>10106200000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>8844400000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>8149600000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>9563700000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>8779100000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>7779600000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>6618900000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>6304500000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2789500000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1963900000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2326600000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>2225500000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1845100000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5189,7 +7155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6341,7 +8307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6369,12 +8335,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>'Net Debt' not found in statements — left blank</t>
         </is>
       </c>
     </row>
